--- a/downloads/contractor-estimate.xlsx
+++ b/downloads/contractor-estimate.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimate" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Estimate'!$A$1:$E$60</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,11 +34,22 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00F97316"/>
-      <sz val="24"/>
+      <sz val="28"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -44,12 +58,19 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00F97316"/>
-      <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
       <sz val="13"/>
     </font>
     <font>
@@ -60,15 +81,24 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
+      <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00F97316"/>
-      <sz val="13"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
+      <sz val="20"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,14 +107,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="00F97316"/>
+        <bgColor rgb="00F97316"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7ED"/>
+        <bgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,38 +133,66 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,570 +555,809 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00F97316"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>📋 Estimate &amp; Bid Template — Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BuiltRight Academy | builtrighthq.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>— HOW TO USE THIS TEMPLATE —</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1. Replace [BRACKETED TEXT] with your company info.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2. Update the estimate number and dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>3. Replace materials and labor items with your actual scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>4. All totals calculate automatically via formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>5. Adjust markup % in the Project Summary section (default: 15%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>6. Adjust tax rate (default: 8.25%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. Customize terms &amp; conditions for your business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>— PRICING TIPS —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• Always include a line item for permits — forgetting this kills margins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>• Use "Miscellaneous supplies" as a catch-all (3-5% of materials).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>• Markup should cover overhead: insurance, truck, tools, office, profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>• 15-25% markup is standard for residential remodeling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>• Include "Unforeseen conditions" clause — it saves you from surprise costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>© 2026 BuiltRight Academy | builtrighthq.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F97316"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
           <t>ESTIMATE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>YOUR COMPANY NAME</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>[YOUR COMPANY NAME]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Estimate #:</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>EST-2026-042</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>123 Main Street, Suite 100</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>[Address] | [Phone] | [Email]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Your City, ST 12345</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>License #: [Your License]</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Valid Until:</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Phone: (555) 123-4567</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Email: info@yourcompany.com</t>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>PREPARED FOR:</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PROJECT:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Robert &amp; Maria Garcia</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Master Bathroom Remodel</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>PREPARED FOR:</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>789 Maple Drive, Austin, TX 78704</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Timeline: 3-4 weeks</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Robert &amp; Linda Chen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>789 Maple Drive</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>(512) 555-8901 | garcia.home@email.com</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Springfield, IL 62704</t>
-        </is>
-      </c>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>MATERIALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>PROJECT: Master Bathroom Remodel</t>
-        </is>
-      </c>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Porcelain tile — 12x24 matte (floor + shower)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D14" s="14">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Vanity — 60" double sink, solid wood</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="18">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>MATERIALS</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Quartz countertop — 60" with undermount cutouts</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>850</v>
+      </c>
+      <c r="D16" s="14">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Shower valve — Moen thermostatic rough-in kit</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>285</v>
+      </c>
+      <c r="D17" s="18">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Porcelain floor tile (12×24) - 80 sq ft</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Tile backer board — 1/2" cement board (10 sheets)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" s="14">
         <f>B18*C18</f>
         <v/>
       </c>
+      <c r="E18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Shower wall tile (subway) - 120 sq ft</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D19" s="12">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Waterproofing membrane — Kerdi (200 sq ft roll)</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>185</v>
+      </c>
+      <c r="D19" s="18">
         <f>B19*C19</f>
         <v/>
       </c>
+      <c r="E19" s="19" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Vanity - 48" double sink</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Toilet — Toto Drake II elongated</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>850</v>
-      </c>
-      <c r="D20" s="9">
+      <c r="C20" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="D20" s="14">
         <f>B20*C20</f>
         <v/>
       </c>
+      <c r="E20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Toilet - Kohler Highline comfort height</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Paint — Benjamin Moore Regal, 2 gal</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="D21" s="18">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Miscellaneous supplies (grout, thin-set, screws, caulk)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="D21" s="12">
-        <f>B21*C21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Shower valve + trim kit (Moen)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>320</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="D22" s="14">
         <f>B22*C22</f>
         <v/>
       </c>
+      <c r="E22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Frameless glass shower door (48")</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D23" s="12">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Exhaust fan - 110 CFM with light</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>175</v>
-      </c>
-      <c r="D24" s="9">
-        <f>B24*C24</f>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Materials Subtotal:</t>
+        </is>
+      </c>
+      <c r="D23" s="21">
+        <f>SUM(D14:D22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Thinset, grout, backer board, supplies</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>280</v>
-      </c>
-      <c r="D25" s="12">
-        <f>B25*C25</f>
-        <v/>
-      </c>
+          <t>LABOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Rate/Hr</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>LABOR</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Demolition &amp; haul-away</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D27" s="14">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Plumbing rough-in</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>85</v>
+      </c>
+      <c r="D28" s="18">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="19" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Demo &amp; haul-away</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Electrical (GFCI outlets, exhaust fan)</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D29" s="14">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Tile installation — floor &amp; shower</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="D30" s="18">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Vanity &amp; countertop install</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" s="14">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Paint — walls &amp; ceiling, 2 coats</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C32" s="18" t="n">
+        <v>55</v>
+      </c>
+      <c r="D32" s="18">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Trim, hardware &amp; final details</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="D29" s="9">
-        <f>B29*C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Plumbing rough-in</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="D30" s="12">
-        <f>B30*C30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Electrical rough-in</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="D31" s="9">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Tile installation (floor + shower)</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="D32" s="12">
-        <f>B32*C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Vanity &amp; fixture install</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="D33" s="9">
+      <c r="D33" s="14">
         <f>B33*C33</f>
         <v/>
       </c>
+      <c r="E33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Painting &amp; trim</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="D34" s="12">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Final clean &amp; punch list</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="D35" s="9">
-        <f>B35*C35</f>
-        <v/>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Labor Subtotal:</t>
+        </is>
+      </c>
+      <c r="D34" s="21">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>PROJECT SUMMARY</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Materials Subtotal:</t>
-        </is>
-      </c>
-      <c r="D37" s="13">
-        <f>SUM(D18:D25)</f>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Materials:</t>
+        </is>
+      </c>
+      <c r="D37" s="22">
+        <f>D23</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Labor Subtotal:</t>
-        </is>
-      </c>
-      <c r="D38" s="13">
-        <f>SUM(D29:D35)</f>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Labor:</t>
+        </is>
+      </c>
+      <c r="D38" s="22">
+        <f>D34</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>Subtotal:</t>
         </is>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="22">
         <f>D37+D38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>Markup (15%):</t>
         </is>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="22">
         <f>D39*0.15</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>Tax (8.25%):</t>
         </is>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="22">
         <f>(D39+D40)*0.0825</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL:</t>
-        </is>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL:</t>
+        </is>
+      </c>
+      <c r="D42" s="24">
         <f>D39+D40+D41</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>TERMS &amp; CONDITIONS</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>1. This estimate is valid for 30 days from the date above.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2. 50% deposit required to schedule work. Balance due upon completion.</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2. 50% deposit required before work begins. Balance due upon completion.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>3. Any changes to scope will be documented via Change Order.</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3. Any changes to the scope of work will be documented via Change Order.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>4. Unforeseen conditions (rot, mold, code issues) billed at T&amp;M.</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4. Unforeseen conditions (rot, mold, code issues) may result in additional charges.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>5. All work guaranteed for 1 year from completion date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>5. All work warranted for 1 year. Manufacturer warranties apply to materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>6. Contractor is licensed, bonded, and insured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>ACCEPTANCE</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Client Signature: ____________________________    Date: ____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Contractor Signature: ________________________    Date: ____________</t>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>By signing below, you accept this estimate and authorize work to begin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Client Signature: ___________________________</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Date: ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Contractor Signature: ________________________</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Date: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
